--- a/data/trans_orig/KIDM_C_3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_3_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>56267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59691</t>
+          <t>59599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66193</t>
+          <t>66028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112529</t>
+          <t>112502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120927</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95395</t>
+          <t>95374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84653</t>
+          <t>84667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90748</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174892</t>
+          <t>175352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184740</t>
+          <t>185051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49323</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55016</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60897</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108594</t>
+          <t>108430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115225</t>
+          <t>115141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70865</t>
+          <t>71419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77516</t>
+          <t>77581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80953</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154982</t>
+          <t>154615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163083</t>
+          <t>163598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267627</t>
+          <t>267539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279758</t>
+          <t>280023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>290262</t>
+          <t>290893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301527</t>
+          <t>301950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>562125</t>
+          <t>562427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>578627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58630</t>
+          <t>58501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61696</t>
+          <t>61809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68844</t>
+          <t>68859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114525</t>
+          <t>114378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126077</t>
+          <t>125959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90229</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>70234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82301</t>
+          <t>81816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154064</t>
+          <t>153416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169801</t>
+          <t>169138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46138</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>56766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56996</t>
+          <t>57256</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>107115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120696</t>
+          <t>120553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31408</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65722</t>
+          <t>65528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77300</t>
+          <t>77233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75123</t>
+          <t>75820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>144328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159528</t>
+          <t>159675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>253780</t>
+          <t>253124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274935</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>274975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295152</t>
+          <t>295013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535547</t>
+          <t>535924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>563964</t>
+          <t>563372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>59564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67084</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57841</t>
+          <t>57686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>66980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>132856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98127</t>
+          <t>98588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85676</t>
+          <t>85614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96239</t>
+          <t>96294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179347</t>
+          <t>178699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193525</t>
+          <t>192231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58108</t>
+          <t>57783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66587</t>
+          <t>66243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61510</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>70771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123658</t>
+          <t>123821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136038</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>28075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84940</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96576</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86951</t>
+          <t>87287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96064</t>
+          <t>95885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175305</t>
+          <t>175336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190447</t>
+          <t>190576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>304730</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323217</t>
+          <t>322406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>323032</t>
+          <t>322663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>614919</t>
+          <t>615268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>640305</t>
+          <t>640333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41444</t>
+          <t>41966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71901</t>
+          <t>71714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99193</t>
+          <t>99346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147371</t>
+          <t>146597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154566</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67212</t>
+          <t>65994</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62121</t>
+          <t>62228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130367</t>
+          <t>130530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135978</t>
+          <t>135973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47224</t>
+          <t>47468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49971</t>
+          <t>49667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>100771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>108332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196989</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206875</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260482</t>
+          <t>260348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>268824</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>459965</t>
+          <t>460629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472950</t>
+          <t>474059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
